--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.30_Q10_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.30_Q10_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02860597215862872</v>
+        <v>0.01590538725266096</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02860597215862872</v>
+        <v>0.01590538725266096</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02837376820844064</v>
+        <v>0.01572571634854045</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02837376820844064</v>
+        <v>0.01572571634854045</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.02777048318225325</v>
+        <v>0.01531028291371847</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02777048318225325</v>
+        <v>0.01531028291371847</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02684060520063458</v>
+        <v>0.01470988514122436</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02684060520063458</v>
+        <v>0.01470988514122436</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02589639008039091</v>
+        <v>0.01411818087059364</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02589639008039091</v>
+        <v>0.01411818087059364</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02516203472703675</v>
+        <v>0.01366953987131912</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02516203472703675</v>
+        <v>0.01366953987131912</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02472762262710671</v>
+        <v>0.01341382412709682</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02472762262710671</v>
+        <v>0.01341382412709682</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02469426319297123</v>
+        <v>0.01340509239943296</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02469426319297123</v>
+        <v>0.01340509239943296</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02496204222978701</v>
+        <v>0.01358416770207603</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02496204222978701</v>
+        <v>0.01358416770207603</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02619363424114796</v>
+        <v>0.01431443796380199</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02619363424114796</v>
+        <v>0.01431443796380199</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02797434004030679</v>
+        <v>0.01536271583323099</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02797434004030679</v>
+        <v>0.01536271583323099</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.03054809767676091</v>
+        <v>0.01686277040135725</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03054809767676091</v>
+        <v>0.01686277040135725</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.03411450615468099</v>
+        <v>0.01892306918492186</v>
       </c>
       <c r="C14" t="n">
-        <v>0.03411450615468099</v>
+        <v>0.01892306918492186</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.03836024713536288</v>
+        <v>0.0213648038202797</v>
       </c>
       <c r="C15" t="n">
-        <v>0.03836024713536288</v>
+        <v>0.0213648038202797</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.04335767892680732</v>
+        <v>0.0242241448172677</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04335767892680732</v>
+        <v>0.0242241448172677</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.04892366700128712</v>
+        <v>0.02739234852458189</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04892366700128712</v>
+        <v>0.02739234852458189</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.05485126869768473</v>
+        <v>0.03074576917293509</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05485126869768473</v>
+        <v>0.03074576917293509</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.06116214244709534</v>
+        <v>0.03429028375748581</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06116214244709534</v>
+        <v>0.03429028375748581</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.06777602879726019</v>
+        <v>0.0379772047122019</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06777602879726019</v>
+        <v>0.0379772047122019</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.07434408967856017</v>
+        <v>0.04160941607341901</v>
       </c>
       <c r="C21" t="n">
-        <v>0.07434408967856017</v>
+        <v>0.04160941607341901</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0807150000501354</v>
+        <v>0.04510677911690375</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0807150000501354</v>
+        <v>0.04510677911690375</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.08695701195358274</v>
+        <v>0.04851724797709239</v>
       </c>
       <c r="C23" t="n">
-        <v>0.08695701195358274</v>
+        <v>0.04851724797709239</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0935421613063001</v>
+        <v>0.05211723385534806</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0935421613063001</v>
+        <v>0.05211723385534806</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1007931430631495</v>
+        <v>0.05610413227582464</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1007931430631495</v>
+        <v>0.05610413227582464</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1090165637636098</v>
+        <v>0.06065905072125959</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1090165637636098</v>
+        <v>0.06065905072125959</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1179680910360467</v>
+        <v>0.06564687107323894</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1179680910360467</v>
+        <v>0.06564687107323894</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1275621242106755</v>
+        <v>0.071021256729723</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1275621242106755</v>
+        <v>0.071021256729723</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1373838453787479</v>
+        <v>0.07655401790379338</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1373838453787479</v>
+        <v>0.07655401790379338</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1470282224127833</v>
+        <v>0.08198968194293417</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1470282224127833</v>
+        <v>0.08198968194293417</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1562052475974441</v>
+        <v>0.08717508246532346</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1562052475974441</v>
+        <v>0.08717508246532346</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
